--- a/audit/assistant-evidence/browser-local/p5-untyped-credit-direct.xlsx
+++ b/audit/assistant-evidence/browser-local/p5-untyped-credit-direct.xlsx
@@ -2190,7 +2190,7 @@
         <v>236</v>
       </c>
       <c r="B5" s="4">
-        <v>46295.823223831016</v>
+        <v>46295.83193892361</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3208,7 +3208,7 @@
     </row>
     <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>46295.823219178244</v>
+        <v>46295.831934270835</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>165</v>
